--- a/Pressure drop/fluid_components.xlsx
+++ b/Pressure drop/fluid_components.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Documents\GitHub\PSPL_Rocket_A\Pressure drop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB713677-E2C8-479E-92E8-C6349F1D90DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38928FC-E66E-4756-BEA3-C5E1343DC995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>Angle [degrees]</t>
   </si>
@@ -55,9 +55,6 @@
     <t>Ball Valve</t>
   </si>
   <si>
-    <t>Fuel</t>
-  </si>
-  <si>
     <t>Bend</t>
   </si>
   <si>
@@ -76,45 +73,15 @@
     <t>LOx Tube 2</t>
   </si>
   <si>
-    <t>LOx Tube to Injector</t>
-  </si>
-  <si>
     <t>LOx Injector Orifices</t>
   </si>
   <si>
     <t>Fuel Tube 1</t>
   </si>
   <si>
-    <t>Fuel Bend 1</t>
-  </si>
-  <si>
     <t>Fuel Tube 2</t>
   </si>
   <si>
-    <t>Fuel Tube 3</t>
-  </si>
-  <si>
-    <t>Fuel Tube 4</t>
-  </si>
-  <si>
-    <t>Fuel Tube 5</t>
-  </si>
-  <si>
-    <t>Fuel Tube 6</t>
-  </si>
-  <si>
-    <t>Fuel Tube 7</t>
-  </si>
-  <si>
-    <t>Fuel Bend 2</t>
-  </si>
-  <si>
-    <t>Fuel Bend 3</t>
-  </si>
-  <si>
-    <t>Fuel Bend 4</t>
-  </si>
-  <si>
     <t>Fuel Run Valve</t>
   </si>
   <si>
@@ -128,13 +95,49 @@
   </si>
   <si>
     <t>Fuel Venturi</t>
+  </si>
+  <si>
+    <t>Oxidizer</t>
+  </si>
+  <si>
+    <t>Fuel Tube to Injector</t>
+  </si>
+  <si>
+    <t>LOx Bend 1</t>
+  </si>
+  <si>
+    <t>LOx Bend 2</t>
+  </si>
+  <si>
+    <t>LOx Tube 3</t>
+  </si>
+  <si>
+    <t>LOx Bend 3</t>
+  </si>
+  <si>
+    <t>LOx Tube 4</t>
+  </si>
+  <si>
+    <t>LOx Bend 4</t>
+  </si>
+  <si>
+    <t>LOx Tube 5</t>
+  </si>
+  <si>
+    <t>LOx Tube 6</t>
+  </si>
+  <si>
+    <t>LOx Tube 7</t>
+  </si>
+  <si>
+    <t>not using venturis!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +147,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="26"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -290,13 +298,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -616,14 +624,15 @@
     <col min="8" max="8" width="23.1796875" style="2" customWidth="1"/>
     <col min="9" max="9" width="19.54296875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="30.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>0</v>
@@ -652,7 +661,7 @@
     </row>
     <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>8</v>
@@ -673,10 +682,13 @@
       <c r="J2" s="9">
         <v>1E-3</v>
       </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="3" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L3" s="7" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>9</v>
@@ -698,7 +710,7 @@
     </row>
     <row r="4" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>8</v>
@@ -722,7 +734,7 @@
     </row>
     <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>10</v>
@@ -748,7 +760,7 @@
     </row>
     <row r="6" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>8</v>
@@ -772,10 +784,10 @@
     </row>
     <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -786,9 +798,9 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="34" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A8" s="16" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -802,7 +814,7 @@
     </row>
     <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>8</v>
@@ -826,10 +838,10 @@
     </row>
     <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="12">
         <v>90</v>
@@ -852,7 +864,7 @@
     </row>
     <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>8</v>
@@ -879,7 +891,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="12">
         <v>90</v>
@@ -902,7 +914,7 @@
     </row>
     <row r="13" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>8</v>
@@ -926,10 +938,10 @@
     </row>
     <row r="14" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="12">
         <v>90</v>
@@ -952,7 +964,7 @@
     </row>
     <row r="15" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>8</v>
@@ -976,10 +988,10 @@
     </row>
     <row r="16" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="12">
         <v>90</v>
@@ -1002,7 +1014,7 @@
     </row>
     <row r="17" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>8</v>
@@ -1023,10 +1035,13 @@
       <c r="J17" s="11">
         <v>1E-3</v>
       </c>
+      <c r="L17" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="18" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L18" s="10" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>9</v>
@@ -1048,7 +1063,7 @@
     </row>
     <row r="19" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>8</v>
@@ -1072,7 +1087,7 @@
     </row>
     <row r="20" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>10</v>
@@ -1098,7 +1113,7 @@
     </row>
     <row r="21" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>8</v>
@@ -1122,10 +1137,10 @@
     </row>
     <row r="22" spans="1:21" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="10" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>

--- a/Pressure drop/fluid_components.xlsx
+++ b/Pressure drop/fluid_components.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Documents\GitHub\PSPL_Rocket_A\Pressure drop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/049800779a5d4222/Documents/GitHub/PSPL_Rocket_A/Pressure drop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB713677-E2C8-479E-92E8-C6349F1D90DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{DB713677-E2C8-479E-92E8-C6349F1D90DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F847EFA4-F8A1-561A-A762-B6F0BCDBD72E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Pressure drop/fluid_components.xlsx
+++ b/Pressure drop/fluid_components.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/049800779a5d4222/Documents/GitHub/PSPL_Rocket_A/Pressure drop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Documents\GitHub\PSPL_Rocket_A\Pressure drop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{DB713677-E2C8-479E-92E8-C6349F1D90DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F847EFA4-F8A1-561A-A762-B6F0BCDBD72E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4910EEE-6DC6-458B-811E-08C3ED42453A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
   <si>
     <t>Angle [degrees]</t>
   </si>
@@ -55,9 +55,6 @@
     <t>Ball Valve</t>
   </si>
   <si>
-    <t>Fuel</t>
-  </si>
-  <si>
     <t>Bend</t>
   </si>
   <si>
@@ -76,45 +73,15 @@
     <t>LOx Tube 2</t>
   </si>
   <si>
-    <t>LOx Tube to Injector</t>
-  </si>
-  <si>
     <t>LOx Injector Orifices</t>
   </si>
   <si>
     <t>Fuel Tube 1</t>
   </si>
   <si>
-    <t>Fuel Bend 1</t>
-  </si>
-  <si>
     <t>Fuel Tube 2</t>
   </si>
   <si>
-    <t>Fuel Tube 3</t>
-  </si>
-  <si>
-    <t>Fuel Tube 4</t>
-  </si>
-  <si>
-    <t>Fuel Tube 5</t>
-  </si>
-  <si>
-    <t>Fuel Tube 6</t>
-  </si>
-  <si>
-    <t>Fuel Tube 7</t>
-  </si>
-  <si>
-    <t>Fuel Bend 2</t>
-  </si>
-  <si>
-    <t>Fuel Bend 3</t>
-  </si>
-  <si>
-    <t>Fuel Bend 4</t>
-  </si>
-  <si>
     <t>Fuel Run Valve</t>
   </si>
   <si>
@@ -128,13 +95,56 @@
   </si>
   <si>
     <t>Fuel Venturi</t>
+  </si>
+  <si>
+    <t>Oxidizer</t>
+  </si>
+  <si>
+    <t>Fuel Tube to Injector</t>
+  </si>
+  <si>
+    <t>LOx Bend 1</t>
+  </si>
+  <si>
+    <t>LOx Bend 2</t>
+  </si>
+  <si>
+    <t>LOx Tube 3</t>
+  </si>
+  <si>
+    <t>LOx Bend 3</t>
+  </si>
+  <si>
+    <t>LOx Tube 4</t>
+  </si>
+  <si>
+    <t>LOx Bend 4</t>
+  </si>
+  <si>
+    <t>LOx Tube 5</t>
+  </si>
+  <si>
+    <t>LOx Tube 6</t>
+  </si>
+  <si>
+    <t>LOx Tube 7</t>
+  </si>
+  <si>
+    <t>not using venturis!</t>
+  </si>
+  <si>
+    <t>not using these components!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,8 +157,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="26"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -162,19 +177,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -243,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -263,40 +272,58 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -616,22 +643,23 @@
     <col min="8" max="8" width="23.1796875" style="2" customWidth="1"/>
     <col min="9" max="9" width="19.54296875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="30.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="6" t="s">
@@ -651,144 +679,151 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15">
         <v>1</v>
       </c>
       <c r="E2" s="14"/>
-      <c r="F2" s="8"/>
+      <c r="F2" s="15"/>
       <c r="G2" s="14"/>
-      <c r="H2" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="I2" s="9">
+      <c r="H2" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="I2" s="19">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="J2" s="9">
-        <v>1E-3</v>
+      <c r="J2" s="22">
+        <v>1E-3</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="7" t="s">
+      <c r="I3" s="20"/>
+      <c r="J3" s="23"/>
+      <c r="L3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
       <c r="P3" s="14"/>
-      <c r="Q3" s="8"/>
+      <c r="Q3" s="15"/>
       <c r="R3" s="14"/>
-      <c r="S3" s="9">
+      <c r="S3" s="13">
         <v>0.75</v>
       </c>
-      <c r="T3" s="9">
+      <c r="T3" s="13">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="U3" s="9">
+      <c r="U3" s="13">
         <v>1E-3</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="I4" s="20"/>
+      <c r="J4" s="23"/>
+      <c r="L4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9">
+      <c r="N4" s="13"/>
+      <c r="O4" s="13">
         <v>0.33</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="9">
+      <c r="P4" s="14"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="13">
         <v>0.75</v>
       </c>
-      <c r="I4" s="9">
+      <c r="T4" s="13">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="J4" s="9">
+      <c r="U4" s="13">
         <v>1E-3</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="13"/>
       <c r="D5" s="14"/>
-      <c r="E5" s="8">
+      <c r="E5" s="15">
         <v>12</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="9">
+      <c r="F5" s="15"/>
+      <c r="G5" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="13">
         <v>0.75</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="19">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="22">
         <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15">
         <v>1</v>
       </c>
       <c r="E6" s="14"/>
-      <c r="F6" s="8"/>
+      <c r="F6" s="15"/>
       <c r="G6" s="14"/>
-      <c r="H6" s="9">
-        <v>0.75</v>
-      </c>
-      <c r="I6" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="J6" s="9">
+      <c r="H6" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="I6" s="19">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J6" s="22">
         <v>1E-3</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="A7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
       <c r="E7" s="14"/>
-      <c r="F7" s="8"/>
+      <c r="F7" s="15"/>
       <c r="G7" s="14"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:21" ht="34" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A8" s="16" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -801,340 +836,345 @@
       <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I9" s="11">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="21">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="24">
         <v>1E-3</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="10" t="s">
+      <c r="A10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="11">
+        <v>90</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="11">
+        <v>3</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I10" s="21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J10" s="24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J11" s="24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="11">
+        <v>90</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11">
+        <v>3</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J12" s="24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J13" s="24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="11">
+        <v>90</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11">
+        <v>3</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J14" s="24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11">
+        <v>3</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I15" s="21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J15" s="24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="11">
+        <v>90</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="11">
+        <v>3</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I16" s="21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J16" s="24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="21">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J17" s="24">
+        <v>1E-3</v>
+      </c>
+      <c r="L17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I18" s="20"/>
+      <c r="J18" s="23"/>
+      <c r="L18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="N18" s="9"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="T18" s="9">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="U18" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9">
+        <v>0.33</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="21">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="J19" s="24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="11">
         <v>12</v>
       </c>
-      <c r="C10" s="12">
-        <v>90</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="12">
-        <v>3</v>
-      </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I10" s="11">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J10" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="10" t="s">
+      <c r="F20" s="11"/>
+      <c r="G20" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I20" s="21">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="J20" s="24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12">
-        <v>3</v>
-      </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I11" s="11">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J11" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="10" t="s">
+      <c r="C21" s="9"/>
+      <c r="D21" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="21">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="J21" s="24">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="12">
-        <v>90</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="12">
-        <v>3</v>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I12" s="11">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J12" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I13" s="11">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J13" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="12">
-        <v>90</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="12">
-        <v>3</v>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I14" s="11">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J14" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12">
-        <v>3</v>
-      </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I15" s="11">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J15" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="12">
-        <v>90</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="12">
-        <v>3</v>
-      </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I16" s="11">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J16" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I17" s="11">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J17" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L18" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="N18" s="11"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="T18" s="11">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="U18" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11">
-        <v>0.33</v>
-      </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="I19" s="11">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="J19" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="12">
-        <v>12</v>
-      </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="H20" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="I20" s="11">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="J20" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="I21" s="11">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="J21" s="11">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Pressure drop/fluid_components.xlsx
+++ b/Pressure drop/fluid_components.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Documents\GitHub\PSPL_Rocket_A\Pressure drop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/049800779a5d4222/Documents/GitHub/PSPL_Rocket_A/Pressure drop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4910EEE-6DC6-458B-811E-08C3ED42453A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{A4910EEE-6DC6-458B-811E-08C3ED42453A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8812C79D-9282-4C6E-813F-BD9CEE7C8C95}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>Angle [degrees]</t>
   </si>
@@ -76,9 +76,6 @@
     <t>LOx Injector Orifices</t>
   </si>
   <si>
-    <t>Fuel Tube 1</t>
-  </si>
-  <si>
     <t>Fuel Tube 2</t>
   </si>
   <si>
@@ -134,6 +131,12 @@
   </si>
   <si>
     <t>not using these components!</t>
+  </si>
+  <si>
+    <t>LOx Tube 8</t>
+  </si>
+  <si>
+    <t>Fuel Tube to Run Valve</t>
   </si>
 </sst>
 </file>
@@ -141,8 +144,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="#,##0.000"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -299,13 +302,13 @@
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -317,13 +320,13 @@
     <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -631,10 +634,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="32.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.1796875" customWidth="1"/>
@@ -651,7 +655,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>0</v>
@@ -680,14 +684,14 @@
     </row>
     <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="15"/>
       <c r="D2" s="15">
-        <v>1</v>
+        <v>4.45</v>
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="15"/>
@@ -695,21 +699,21 @@
       <c r="H2" s="13">
         <v>0.5</v>
       </c>
-      <c r="I2" s="19">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J2" s="22">
+      <c r="I2" s="16">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="J2" s="19">
         <v>1E-3</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I3" s="20"/>
-      <c r="J3" s="23"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="20"/>
       <c r="L3" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M3" s="12" t="s">
         <v>9</v>
@@ -730,10 +734,10 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I4" s="20"/>
-      <c r="J4" s="23"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="20"/>
       <c r="L4" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>8</v>
@@ -757,7 +761,7 @@
     </row>
     <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>10</v>
@@ -769,45 +773,45 @@
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="13">
-        <v>0.5</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H5" s="13">
         <v>0.75</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="16">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5" s="19">
         <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="15"/>
       <c r="G6" s="14"/>
       <c r="H6" s="13">
-        <v>0.375</v>
-      </c>
-      <c r="I6" s="19">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J6" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="16">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="J6" s="19">
         <v>1E-3</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>12</v>
@@ -822,18 +826,18 @@
       <c r="J7" s="13"/>
     </row>
     <row r="8" spans="1:21" ht="34" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A8" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="18"/>
+      <c r="A8" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="24"/>
     </row>
     <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
@@ -852,16 +856,16 @@
       <c r="H9" s="9">
         <v>0.5</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="18">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="21">
         <v>1E-3</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>11</v>
@@ -878,10 +882,10 @@
       <c r="H10" s="9">
         <v>0.5</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="18">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="21">
         <v>1E-3</v>
       </c>
     </row>
@@ -902,16 +906,16 @@
       <c r="H11" s="9">
         <v>0.5</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="18">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="21">
         <v>1E-3</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>11</v>
@@ -928,16 +932,16 @@
       <c r="H12" s="9">
         <v>0.5</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="18">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="21">
         <v>1E-3</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>8</v>
@@ -952,16 +956,16 @@
       <c r="H13" s="9">
         <v>0.5</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="18">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="21">
         <v>1E-3</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -978,16 +982,16 @@
       <c r="H14" s="9">
         <v>0.5</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="18">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="J14" s="24">
+      <c r="J14" s="21">
         <v>1E-3</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>8</v>
@@ -1002,42 +1006,40 @@
       <c r="H15" s="9">
         <v>0.5</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="18">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="J15" s="24">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J15" s="21">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="11">
-        <v>90</v>
-      </c>
-      <c r="D16" s="10"/>
+        <v>8</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9">
+        <v>0.5</v>
+      </c>
       <c r="E16" s="10"/>
-      <c r="F16" s="11">
-        <v>3</v>
-      </c>
+      <c r="F16" s="11"/>
       <c r="G16" s="10"/>
       <c r="H16" s="9">
         <v>0.5</v>
       </c>
-      <c r="I16" s="21">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J16" s="24">
+      <c r="I16" s="18">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="J16" s="21">
         <v>1E-3</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>8</v>
@@ -1052,21 +1054,21 @@
       <c r="H17" s="9">
         <v>0.5</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="18">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="J17" s="24">
+      <c r="J17" s="21">
         <v>1E-3</v>
       </c>
       <c r="L17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I18" s="20"/>
-      <c r="J18" s="23"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="20"/>
       <c r="L18" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M18" s="8" t="s">
         <v>9</v>
@@ -1088,7 +1090,7 @@
     </row>
     <row r="19" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>8</v>
@@ -1103,10 +1105,10 @@
       <c r="H19" s="9">
         <v>0.5</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="18">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="J19" s="24">
+      <c r="J19" s="21">
         <v>1E-3</v>
       </c>
     </row>
@@ -1129,23 +1131,23 @@
       <c r="H20" s="9">
         <v>0.5</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="18">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="21">
         <v>1E-3</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="11"/>
@@ -1153,28 +1155,78 @@
       <c r="H21" s="9">
         <v>0.5</v>
       </c>
-      <c r="I21" s="21">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="J21" s="24">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="I21" s="18">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="J21" s="21">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="11">
+        <v>45</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="11">
+        <v>3</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I22" s="18">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="J22" s="21">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I23" s="18">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="J23" s="21">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B24" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="24"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Pressure drop/fluid_components.xlsx
+++ b/Pressure drop/fluid_components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/049800779a5d4222/Documents/GitHub/PSPL_Rocket_A/Pressure drop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{A4910EEE-6DC6-458B-811E-08C3ED42453A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8812C79D-9282-4C6E-813F-BD9CEE7C8C95}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:1_{A4910EEE-6DC6-458B-811E-08C3ED42453A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{294190E9-C037-4CFA-8209-DCCC7668EA74}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>Angle [degrees]</t>
   </si>
@@ -88,9 +88,6 @@
     <t>Part Type</t>
   </si>
   <si>
-    <t>LOx Venturi</t>
-  </si>
-  <si>
     <t>Fuel Venturi</t>
   </si>
   <si>
@@ -106,37 +103,25 @@
     <t>LOx Bend 2</t>
   </si>
   <si>
-    <t>LOx Tube 3</t>
-  </si>
-  <si>
     <t>LOx Bend 3</t>
   </si>
   <si>
-    <t>LOx Tube 4</t>
-  </si>
-  <si>
     <t>LOx Bend 4</t>
   </si>
   <si>
-    <t>LOx Tube 5</t>
-  </si>
-  <si>
-    <t>LOx Tube 6</t>
-  </si>
-  <si>
-    <t>LOx Tube 7</t>
-  </si>
-  <si>
     <t>not using venturis!</t>
   </si>
   <si>
     <t>not using these components!</t>
   </si>
   <si>
-    <t>LOx Tube 8</t>
-  </si>
-  <si>
     <t>Fuel Tube to Run Valve</t>
+  </si>
+  <si>
+    <t>LOx Straight 1</t>
+  </si>
+  <si>
+    <t>LOx Bend 5</t>
   </si>
 </sst>
 </file>
@@ -634,7 +619,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.7265625" style="1" customWidth="1"/>
@@ -684,7 +669,7 @@
     </row>
     <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>8</v>
@@ -706,14 +691,14 @@
         <v>1E-3</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="I3" s="17"/>
       <c r="J3" s="20"/>
       <c r="L3" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M3" s="12" t="s">
         <v>9</v>
@@ -787,7 +772,7 @@
     </row>
     <row r="6" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>8</v>
@@ -827,7 +812,7 @@
     </row>
     <row r="8" spans="1:21" ht="34" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A8" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
@@ -841,23 +826,25 @@
     </row>
     <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9">
-        <v>0.5</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C9" s="11">
+        <v>45</v>
+      </c>
+      <c r="D9" s="10"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
+      <c r="F9" s="11">
+        <v>3</v>
+      </c>
       <c r="G9" s="10"/>
       <c r="H9" s="9">
-        <v>0.5</v>
+        <v>1.01</v>
       </c>
       <c r="I9" s="18">
-        <v>4.9000000000000002E-2</v>
+        <v>0.25</v>
       </c>
       <c r="J9" s="21">
         <v>1E-3</v>
@@ -871,7 +858,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="11">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -880,10 +867,10 @@
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="9">
-        <v>0.5</v>
+        <v>1.01</v>
       </c>
       <c r="I10" s="18">
-        <v>4.9000000000000002E-2</v>
+        <v>0.25</v>
       </c>
       <c r="J10" s="21">
         <v>1E-3</v>
@@ -891,26 +878,29 @@
     </row>
     <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11">
-        <v>3</v>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9">
+        <v>11</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
       <c r="G11" s="10"/>
       <c r="H11" s="9">
-        <v>0.5</v>
+        <v>1.01</v>
       </c>
       <c r="I11" s="18">
-        <v>4.9000000000000002E-2</v>
+        <v>0.25</v>
       </c>
       <c r="J11" s="21">
         <v>1E-3</v>
+      </c>
+      <c r="L11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -921,7 +911,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="11">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -930,10 +920,10 @@
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="9">
-        <v>0.5</v>
+        <v>1.01</v>
       </c>
       <c r="I12" s="18">
-        <v>4.9000000000000002E-2</v>
+        <v>0.25</v>
       </c>
       <c r="J12" s="21">
         <v>1E-3</v>
@@ -944,20 +934,22 @@
         <v>28</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9">
-        <v>0.75</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C13" s="11">
+        <v>45</v>
+      </c>
+      <c r="D13" s="10"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
+      <c r="F13" s="11">
+        <v>3</v>
+      </c>
       <c r="G13" s="10"/>
       <c r="H13" s="9">
-        <v>0.5</v>
+        <v>1.01</v>
       </c>
       <c r="I13" s="18">
-        <v>4.9000000000000002E-2</v>
+        <v>0.25</v>
       </c>
       <c r="J13" s="21">
         <v>1E-3</v>
@@ -965,40 +957,40 @@
     </row>
     <row r="14" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="11">
-        <v>90</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C14" s="9"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="11">
-        <v>3</v>
-      </c>
-      <c r="G14" s="10"/>
+      <c r="E14" s="11">
+        <v>12</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H14" s="9">
         <v>0.5</v>
       </c>
       <c r="I14" s="18">
-        <v>4.9000000000000002E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="J14" s="21">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11">
-        <v>3</v>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9">
+        <v>2.5</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="11"/>
@@ -1007,46 +999,48 @@
         <v>0.5</v>
       </c>
       <c r="I15" s="18">
-        <v>4.9000000000000002E-2</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="J15" s="21">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9">
-        <v>0.5</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C16" s="11">
+        <v>45</v>
+      </c>
+      <c r="D16" s="10"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
+      <c r="F16" s="11">
+        <v>3</v>
+      </c>
       <c r="G16" s="10"/>
       <c r="H16" s="9">
         <v>0.5</v>
       </c>
       <c r="I16" s="18">
-        <v>6.5000000000000002E-2</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="J16" s="21">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="11"/>
@@ -1055,178 +1049,27 @@
         <v>0.5</v>
       </c>
       <c r="I17" s="18">
-        <v>4.9000000000000002E-2</v>
+        <v>8.3000000000000004E-2</v>
       </c>
       <c r="J17" s="21">
         <v>1E-3</v>
       </c>
-      <c r="L17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I18" s="17"/>
-      <c r="J18" s="20"/>
-      <c r="L18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="N18" s="9"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="9">
-        <v>0.75</v>
-      </c>
-      <c r="T18" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="U18" s="9">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9">
-        <v>0.33</v>
-      </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="18">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="J19" s="21">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="11">
+    </row>
+    <row r="18" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="H20" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="I20" s="18">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="J20" s="21">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="E21" s="10"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="I21" s="18">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="J21" s="21">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="11">
-        <v>45</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="11">
-        <v>3</v>
-      </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="I22" s="18">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="J22" s="21">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="I23" s="18">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="J23" s="21">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="21"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
